--- a/backend/Rwanda/upload-CleanStep.xlsx
+++ b/backend/Rwanda/upload-CleanStep.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8954da175e61d5af/Escritorio/IIT/CC-WBT/backend/LPG testing/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8954da175e61d5af/Escritorio/IIT/CC-WBT/backend/Rwanda/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{8B2187DB-C16E-486E-8A9E-03C236752202}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D07A24C6-F443-40C5-BBF5-85F3138D932D}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{8B2187DB-C16E-486E-8A9E-03C236752202}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D3767058-31C6-4B6F-B44E-81A039B927CD}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1515,40 +1515,40 @@
         <v>6</v>
       </c>
       <c r="C4" s="24">
-        <v>0</v>
+        <v>850</v>
       </c>
       <c r="D4" s="24">
-        <v>0</v>
+        <v>875</v>
       </c>
       <c r="E4" s="24">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="F4" s="24">
-        <v>0</v>
+        <v>925</v>
       </c>
       <c r="G4" s="24">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="H4" s="24">
-        <v>0</v>
+        <v>975</v>
       </c>
       <c r="I4" s="24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J4" s="24">
-        <v>0</v>
+        <v>1025</v>
       </c>
       <c r="K4" s="24">
-        <v>0</v>
+        <v>1050</v>
       </c>
       <c r="L4" s="24">
-        <v>0</v>
+        <v>1075</v>
       </c>
       <c r="M4" s="24">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="N4" s="24">
-        <v>0</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">

--- a/backend/Rwanda/upload-CleanStep.xlsx
+++ b/backend/Rwanda/upload-CleanStep.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8954da175e61d5af/Escritorio/IIT/CC-WBT/backend/Rwanda/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{8B2187DB-C16E-486E-8A9E-03C236752202}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D3767058-31C6-4B6F-B44E-81A039B927CD}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="13_ncr:1_{8B2187DB-C16E-486E-8A9E-03C236752202}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57202B86-AB0A-4834-BA16-D71D158D1E46}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Electricity" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="20">
   <si>
     <t>Type - Inputs</t>
   </si>
@@ -44,9 +44,6 @@
   </si>
   <si>
     <t>Units</t>
-  </si>
-  <si>
-    <t>Baseline</t>
   </si>
   <si>
     <t>GRID</t>
@@ -339,6 +336,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -620,8 +621,8 @@
       <c r="C1" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
-        <v>3</v>
+      <c r="D1" s="6">
+        <v>2023</v>
       </c>
       <c r="E1" s="6">
         <v>2024</v>
@@ -659,577 +660,577 @@
     </row>
     <row r="2" spans="1:15" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="C2" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="11" t="s">
-        <v>6</v>
-      </c>
       <c r="D2" s="10">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E2" s="10">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F2" s="10">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G2" s="10">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H2" s="10">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I2" s="10">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J2" s="10">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K2" s="10">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L2" s="10">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M2" s="10">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N2" s="10">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O2" s="10">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B3" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="11" t="s">
-        <v>8</v>
-      </c>
       <c r="D3" s="10">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E3" s="10">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F3" s="10">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G3" s="10">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H3" s="10">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I3" s="10">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J3" s="10">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K3" s="10">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L3" s="10">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M3" s="10">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N3" s="10">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O3" s="10">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="10">
-        <v>0</v>
-      </c>
-      <c r="E4" s="10">
-        <v>0</v>
-      </c>
-      <c r="F4" s="10">
-        <v>0</v>
-      </c>
-      <c r="G4" s="10">
-        <v>0</v>
-      </c>
-      <c r="H4" s="10">
-        <v>0</v>
-      </c>
-      <c r="I4" s="10">
-        <v>0</v>
-      </c>
-      <c r="J4" s="10">
-        <v>0</v>
-      </c>
-      <c r="K4" s="10">
-        <v>0</v>
-      </c>
-      <c r="L4" s="10">
-        <v>0</v>
-      </c>
-      <c r="M4" s="10">
-        <v>0</v>
-      </c>
-      <c r="N4" s="10">
-        <v>0</v>
-      </c>
-      <c r="O4" s="10">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="D4" s="24">
+        <v>850</v>
+      </c>
+      <c r="E4" s="24">
+        <v>875</v>
+      </c>
+      <c r="F4" s="24">
+        <v>900</v>
+      </c>
+      <c r="G4" s="24">
+        <v>925</v>
+      </c>
+      <c r="H4" s="24">
+        <v>950</v>
+      </c>
+      <c r="I4" s="24">
+        <v>975</v>
+      </c>
+      <c r="J4" s="24">
+        <v>1000</v>
+      </c>
+      <c r="K4" s="24">
+        <v>1025</v>
+      </c>
+      <c r="L4" s="24">
+        <v>1050</v>
+      </c>
+      <c r="M4" s="24">
+        <v>1075</v>
+      </c>
+      <c r="N4" s="24">
+        <v>1100</v>
+      </c>
+      <c r="O4" s="24">
+        <v>1125</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="14" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="H5" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="I5" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="J5" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="K5" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="L5" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="M5" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="N5" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="O5" s="15" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="D5" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="H5" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="I5" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="J5" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="K5" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="L5" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="M5" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="N5" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="O5" s="25" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="16" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B6" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="10">
-        <v>0</v>
-      </c>
-      <c r="E6" s="10">
-        <v>0</v>
-      </c>
-      <c r="F6" s="10">
-        <v>0</v>
-      </c>
-      <c r="G6" s="10">
-        <v>0</v>
-      </c>
-      <c r="H6" s="10">
-        <v>0</v>
-      </c>
-      <c r="I6" s="10">
-        <v>0</v>
-      </c>
-      <c r="J6" s="10">
-        <v>0</v>
-      </c>
-      <c r="K6" s="10">
-        <v>0</v>
-      </c>
-      <c r="L6" s="10">
-        <v>0</v>
-      </c>
-      <c r="M6" s="10">
-        <v>0</v>
-      </c>
-      <c r="N6" s="10">
-        <v>0</v>
-      </c>
-      <c r="O6" s="10">
-        <v>0</v>
+      <c r="D6" s="26">
+        <v>9.4411982377545986E-2</v>
+      </c>
+      <c r="E6" s="26">
+        <v>0.17910918254928315</v>
+      </c>
+      <c r="F6" s="26">
+        <v>0.17731809072379034</v>
+      </c>
+      <c r="G6" s="26">
+        <v>0.17554490981655244</v>
+      </c>
+      <c r="H6" s="26">
+        <v>0.17378946071838691</v>
+      </c>
+      <c r="I6" s="26">
+        <v>0.17205156611120306</v>
+      </c>
+      <c r="J6" s="26">
+        <v>0.13007825774755519</v>
+      </c>
+      <c r="K6" s="26">
+        <v>8.8726452122599442E-2</v>
+      </c>
+      <c r="L6" s="26">
+        <v>8.783918760137345E-2</v>
+      </c>
+      <c r="M6" s="26">
+        <v>8.6960795725359696E-2</v>
+      </c>
+      <c r="N6" s="26">
+        <v>8.609118776810612E-2</v>
+      </c>
+      <c r="O6" s="26">
+        <v>7.9676328396537641E-2</v>
       </c>
     </row>
     <row r="7" spans="1:15" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="16" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" s="10">
-        <v>0</v>
-      </c>
-      <c r="E7" s="10">
-        <v>0</v>
-      </c>
-      <c r="F7" s="10">
-        <v>0</v>
-      </c>
-      <c r="G7" s="10">
-        <v>0</v>
-      </c>
-      <c r="H7" s="10">
-        <v>0</v>
-      </c>
-      <c r="I7" s="10">
-        <v>0</v>
-      </c>
-      <c r="J7" s="10">
-        <v>0</v>
-      </c>
-      <c r="K7" s="10">
-        <v>0</v>
-      </c>
-      <c r="L7" s="10">
-        <v>0</v>
-      </c>
-      <c r="M7" s="10">
-        <v>0</v>
-      </c>
-      <c r="N7" s="10">
-        <v>0</v>
-      </c>
-      <c r="O7" s="10">
+        <v>12</v>
+      </c>
+      <c r="D7" s="24">
+        <v>0</v>
+      </c>
+      <c r="E7" s="24">
+        <v>0</v>
+      </c>
+      <c r="F7" s="24">
+        <v>0</v>
+      </c>
+      <c r="G7" s="24">
+        <v>0</v>
+      </c>
+      <c r="H7" s="24">
+        <v>0</v>
+      </c>
+      <c r="I7" s="24">
+        <v>0</v>
+      </c>
+      <c r="J7" s="24">
+        <v>0</v>
+      </c>
+      <c r="K7" s="24">
+        <v>0</v>
+      </c>
+      <c r="L7" s="24">
+        <v>0</v>
+      </c>
+      <c r="M7" s="24">
+        <v>0</v>
+      </c>
+      <c r="N7" s="24">
+        <v>0</v>
+      </c>
+      <c r="O7" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:15" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="16" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" s="10">
-        <v>0</v>
-      </c>
-      <c r="E8" s="10">
-        <v>0</v>
-      </c>
-      <c r="F8" s="10">
-        <v>0</v>
-      </c>
-      <c r="G8" s="10">
-        <v>0</v>
-      </c>
-      <c r="H8" s="10">
-        <v>0</v>
-      </c>
-      <c r="I8" s="10">
-        <v>0</v>
-      </c>
-      <c r="J8" s="10">
-        <v>0</v>
-      </c>
-      <c r="K8" s="10">
-        <v>0</v>
-      </c>
-      <c r="L8" s="10">
-        <v>0</v>
-      </c>
-      <c r="M8" s="10">
-        <v>0</v>
-      </c>
-      <c r="N8" s="10">
-        <v>0</v>
-      </c>
-      <c r="O8" s="10">
-        <v>0</v>
+        <v>12</v>
+      </c>
+      <c r="D8" s="24">
+        <v>4.3214328362237504</v>
+      </c>
+      <c r="E8" s="24">
+        <v>6.2363090899502751</v>
+      </c>
+      <c r="F8" s="24">
+        <v>8.8215903075601076</v>
+      </c>
+      <c r="G8" s="24">
+        <v>11.354542269908746</v>
+      </c>
+      <c r="H8" s="24">
+        <v>13.835953033979656</v>
+      </c>
+      <c r="I8" s="24">
+        <v>16.266600128542159</v>
+      </c>
+      <c r="J8" s="24">
+        <v>18.647250685910016</v>
+      </c>
+      <c r="K8" s="24">
+        <v>19.398693999490821</v>
+      </c>
+      <c r="L8" s="24">
+        <v>19.740377685024988</v>
+      </c>
+      <c r="M8" s="24">
+        <v>20.073287827448521</v>
+      </c>
+      <c r="N8" s="24">
+        <v>20.397565729255085</v>
+      </c>
+      <c r="O8" s="24">
+        <v>20.713350744242767</v>
       </c>
     </row>
     <row r="9" spans="1:15" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="16" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B9" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" s="19">
-        <v>0</v>
-      </c>
-      <c r="E9" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="G9" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="H9" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="I9" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="J9" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="K9" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="L9" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="M9" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="N9" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="O9" s="19" t="s">
-        <v>11</v>
+      <c r="D9" s="27">
+        <v>15</v>
+      </c>
+      <c r="E9" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="H9" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="I9" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="J9" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="K9" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="L9" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="M9" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="N9" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="O9" s="27" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:15" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B10" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="11" t="s">
-        <v>6</v>
-      </c>
       <c r="D10" s="10">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E10" s="10">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F10" s="10">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G10" s="10">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H10" s="10">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I10" s="10">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J10" s="10">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K10" s="10">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L10" s="10">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M10" s="10">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N10" s="10">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O10" s="10">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:15" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="11" t="s">
-        <v>8</v>
-      </c>
       <c r="D11" s="10">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E11" s="10">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F11" s="10">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G11" s="10">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H11" s="10">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I11" s="10">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J11" s="10">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K11" s="10">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L11" s="10">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M11" s="10">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="N11" s="10">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O11" s="10">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:15" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G12" s="15" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H12" s="15" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I12" s="15" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J12" s="15" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L12" s="15" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M12" s="15" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N12" s="15" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O12" s="15" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:15" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B13" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="11" t="s">
-        <v>13</v>
-      </c>
       <c r="D13" s="10">
-        <v>0</v>
+        <v>650</v>
       </c>
       <c r="E13" s="10">
-        <v>0</v>
+        <v>650</v>
       </c>
       <c r="F13" s="10">
-        <v>0</v>
+        <v>650</v>
       </c>
       <c r="G13" s="10">
-        <v>0</v>
+        <v>650</v>
       </c>
       <c r="H13" s="10">
-        <v>0</v>
+        <v>650</v>
       </c>
       <c r="I13" s="10">
-        <v>0</v>
+        <v>650</v>
       </c>
       <c r="J13" s="10">
-        <v>0</v>
+        <v>650</v>
       </c>
       <c r="K13" s="10">
-        <v>0</v>
+        <v>650</v>
       </c>
       <c r="L13" s="10">
-        <v>0</v>
+        <v>650</v>
       </c>
       <c r="M13" s="10">
-        <v>0</v>
+        <v>650</v>
       </c>
       <c r="N13" s="10">
-        <v>0</v>
+        <v>650</v>
       </c>
       <c r="O13" s="10">
-        <v>0</v>
+        <v>650</v>
       </c>
     </row>
     <row r="14" spans="1:15" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D14" s="10">
         <v>0</v>
@@ -1270,96 +1271,96 @@
     </row>
     <row r="15" spans="1:15" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D15" s="10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E15" s="10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F15" s="10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G15" s="10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H15" s="10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I15" s="10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J15" s="10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K15" s="10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L15" s="10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M15" s="10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N15" s="10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O15" s="10">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:15" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B16" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="D16" s="19">
         <v>17</v>
       </c>
-      <c r="D16" s="19">
-        <v>0</v>
-      </c>
       <c r="E16" s="19" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F16" s="19" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G16" s="19" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H16" s="19" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I16" s="19" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J16" s="19" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K16" s="19" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L16" s="19" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M16" s="19" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N16" s="19" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O16" s="19" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1421,10 +1422,10 @@
     </row>
     <row r="2" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="23" t="s">
         <v>5</v>
-      </c>
-      <c r="B2" s="23" t="s">
-        <v>6</v>
       </c>
       <c r="C2" s="24">
         <v>0</v>
@@ -1465,10 +1466,10 @@
     </row>
     <row r="3" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="23" t="s">
         <v>7</v>
-      </c>
-      <c r="B3" s="23" t="s">
-        <v>8</v>
       </c>
       <c r="C3" s="24">
         <v>0</v>
@@ -1509,10 +1510,10 @@
     </row>
     <row r="4" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C4" s="24">
         <v>850</v>
@@ -1553,54 +1554,54 @@
     </row>
     <row r="5" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="20" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D5" s="25" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E5" s="25" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F5" s="25" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G5" s="25" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H5" s="25" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I5" s="25" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J5" s="25" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K5" s="25" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L5" s="25" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M5" s="25" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N5" s="25" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="23" t="s">
         <v>12</v>
-      </c>
-      <c r="B6" s="23" t="s">
-        <v>13</v>
       </c>
       <c r="C6" s="26">
         <v>9.4411982377545986E-2</v>
@@ -1641,10 +1642,10 @@
     </row>
     <row r="7" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="16" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C7" s="24">
         <v>0</v>
@@ -1685,10 +1686,10 @@
     </row>
     <row r="8" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C8" s="24">
         <v>4.3214328362237504</v>
@@ -1729,46 +1730,46 @@
     </row>
     <row r="9" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="23" t="s">
         <v>16</v>
-      </c>
-      <c r="B9" s="23" t="s">
-        <v>17</v>
       </c>
       <c r="C9" s="27">
         <v>15</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F9" s="27" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G9" s="27" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H9" s="27" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I9" s="27" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J9" s="27" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K9" s="27" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L9" s="27" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M9" s="27" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N9" s="27" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1828,10 +1829,10 @@
     </row>
     <row r="2" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>19</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>20</v>
       </c>
       <c r="C2" s="22">
         <v>21.610541230631693</v>
